--- a/Routes.xlsx
+++ b/Routes.xlsx
@@ -18216,7 +18216,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>ROM414</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>ROM414</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -18266,12 +18266,12 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>No route from ROM421</t>
+          <t>No route from ROM414</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>ROM414</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -18290,17 +18290,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>ROM414</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>ROM414</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -18340,12 +18340,12 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>No route from ROM292</t>
+          <t>No route from ROM414</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>ROM414</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -18369,12 +18369,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -18438,7 +18438,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>AIF101</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18448,22 +18448,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -18473,34 +18473,38 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>No route from ROM421</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>ROM421</t>
-        </is>
-      </c>
-      <c r="M234" t="n">
-        <v/>
-      </c>
-      <c r="N234" t="n">
-        <v/>
+          <t>AIF101</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>JFH102</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="O234" t="n">
         <v/>
@@ -18512,32 +18516,32 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>AIF101</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -18547,34 +18551,38 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>No route from ROM292</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>ROM292</t>
-        </is>
-      </c>
-      <c r="M235" t="n">
-        <v/>
-      </c>
-      <c r="N235" t="n">
-        <v/>
+          <t>AIF101</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>JFH102</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="O235" t="n">
         <v/>
@@ -18586,32 +18594,32 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ROM414</t>
+          <t>ARIS01</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -18621,31 +18629,33 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>ROM414</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>No route from ROM414</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>ROM414</t>
-        </is>
-      </c>
-      <c r="M236" t="n">
-        <v/>
+          <t>ARIS01</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="N236" t="n">
         <v/>
@@ -18660,32 +18670,32 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>ARIS01</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -18695,31 +18705,33 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>ROM421</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>No route from ROM421</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>ROM421</t>
-        </is>
-      </c>
-      <c r="M237" t="n">
-        <v/>
+          <t>ARIS01</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="N237" t="n">
         <v/>
@@ -18734,7 +18746,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>ARIS01</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18744,22 +18756,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -18769,31 +18781,33 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>ROM292</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>No route from ROM292</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>ROM292</t>
-        </is>
-      </c>
-      <c r="M238" t="n">
-        <v/>
+          <t>ARIS01</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="N238" t="n">
         <v/>
@@ -18808,32 +18822,32 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ROM414</t>
+          <t>BBKE01</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Isolated</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -18843,34 +18857,38 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>ROM414</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Broken</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>No route from ROM414</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>ROM414</t>
-        </is>
-      </c>
-      <c r="M239" t="n">
-        <v/>
-      </c>
-      <c r="N239" t="n">
-        <v/>
+          <t>BBKE01</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>ARIS01</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="O239" t="n">
         <v/>
@@ -18882,7 +18900,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>AIF101</t>
+          <t>BBKE01</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18892,7 +18910,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -18917,7 +18935,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -18937,17 +18955,17 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>AIF101</t>
+          <t>BBKE01</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>ARIS01</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="O240" t="n">
@@ -18960,7 +18978,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>AIF101</t>
+          <t>BBKE01</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18970,7 +18988,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -18995,7 +19013,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -19015,17 +19033,17 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>AIF101</t>
+          <t>BBKE01</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>ARIS01</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="O241" t="n">
@@ -19038,7 +19056,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ARIS01</t>
+          <t>DJQF02</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19048,7 +19066,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -19073,7 +19091,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -19093,19 +19111,23 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>ARIS01</t>
+          <t>DJQF02</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>EPG105</t>
-        </is>
-      </c>
-      <c r="N242" t="n">
-        <v/>
-      </c>
-      <c r="O242" t="n">
-        <v/>
+          <t>KGZK01</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>DJQF03</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="P242" t="n">
         <v/>
@@ -19114,7 +19136,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ARIS01</t>
+          <t>DJQF02</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19124,7 +19146,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -19149,7 +19171,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -19169,19 +19191,23 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>ARIS01</t>
+          <t>DJQF02</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>EPG105</t>
-        </is>
-      </c>
-      <c r="N243" t="n">
-        <v/>
-      </c>
-      <c r="O243" t="n">
-        <v/>
+          <t>KGZK01</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>DJQF03</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="P243" t="n">
         <v/>
@@ -19190,7 +19216,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ARIS01</t>
+          <t>DJQF02</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19200,7 +19226,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -19225,7 +19251,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -19245,19 +19271,23 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>ARIS01</t>
+          <t>DJQF02</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>EPG105</t>
-        </is>
-      </c>
-      <c r="N244" t="n">
-        <v/>
-      </c>
-      <c r="O244" t="n">
-        <v/>
+          <t>KGZK01</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>DJQF03</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="P244" t="n">
         <v/>
@@ -19266,7 +19296,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BBKE01</t>
+          <t>DJQF03</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19276,7 +19306,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -19301,7 +19331,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -19321,18 +19351,16 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>BBKE01</t>
+          <t>DJQF03</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>ARIS01</t>
-        </is>
-      </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>ZMA105</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v/>
       </c>
       <c r="O245" t="n">
         <v/>
@@ -19344,7 +19372,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BBKE01</t>
+          <t>DJQF03</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19354,7 +19382,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -19379,7 +19407,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -19399,18 +19427,16 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>BBKE01</t>
+          <t>DJQF03</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>ARIS01</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>ZMA105</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v/>
       </c>
       <c r="O246" t="n">
         <v/>
@@ -19422,7 +19448,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BBKE01</t>
+          <t>DJQF03</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19432,7 +19458,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -19457,7 +19483,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -19477,18 +19503,16 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>BBKE01</t>
+          <t>DJQF03</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>ARIS01</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>ZMA105</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v/>
       </c>
       <c r="O247" t="n">
         <v/>
@@ -19500,7 +19524,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DJQF02</t>
+          <t>DJQF04</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19510,7 +19534,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -19555,23 +19579,21 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>DJQF02</t>
+          <t>DJQF04</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr">
-        <is>
           <t>ZMA105</t>
         </is>
+      </c>
+      <c r="O248" t="n">
+        <v/>
       </c>
       <c r="P248" t="n">
         <v/>
@@ -19580,7 +19602,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DJQF02</t>
+          <t>DJQF04</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19590,7 +19612,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -19635,23 +19657,21 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>DJQF02</t>
+          <t>DJQF04</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="O249" t="inlineStr">
-        <is>
           <t>ZMA105</t>
         </is>
+      </c>
+      <c r="O249" t="n">
+        <v/>
       </c>
       <c r="P249" t="n">
         <v/>
@@ -19660,7 +19680,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DJQF02</t>
+          <t>DJQF04</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19670,7 +19690,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -19715,23 +19735,21 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>DJQF02</t>
+          <t>DJQF04</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
           <t>ZMA105</t>
         </is>
+      </c>
+      <c r="O250" t="n">
+        <v/>
       </c>
       <c r="P250" t="n">
         <v/>
@@ -19740,7 +19758,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>DJQF03</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19750,32 +19768,32 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -19795,12 +19813,12 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>DJQF03</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="N251" t="n">
@@ -19816,7 +19834,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>DJQF03</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19826,37 +19844,37 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -19866,18 +19884,16 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>EPG101</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
+        <v/>
       </c>
       <c r="N252" t="n">
         <v/>
@@ -19892,7 +19908,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>DJQF03</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19902,37 +19918,37 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -19942,18 +19958,16 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>EPG101</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v/>
       </c>
       <c r="N253" t="n">
         <v/>
@@ -19968,7 +19982,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>DJQF04</t>
+          <t>EPG107</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19978,7 +19992,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -20003,7 +20017,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -20023,18 +20037,16 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>DJQF04</t>
+          <t>EPG107</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>JXHV01</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>EPG105</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v/>
       </c>
       <c r="O254" t="n">
         <v/>
@@ -20046,7 +20058,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>DJQF04</t>
+          <t>EPG107</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20056,7 +20068,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -20081,7 +20093,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -20101,18 +20113,16 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>DJQF04</t>
+          <t>EPG107</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>JXHV01</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>EPG105</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v/>
       </c>
       <c r="O255" t="n">
         <v/>
@@ -20124,7 +20134,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DJQF04</t>
+          <t>EPG107</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20134,7 +20144,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -20159,7 +20169,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -20179,18 +20189,16 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>DJQF04</t>
+          <t>EPG107</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>JXHV01</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>EPG105</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v/>
       </c>
       <c r="O256" t="n">
         <v/>
@@ -20202,7 +20210,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20212,7 +20220,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -20257,7 +20265,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20278,17 +20286,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -20313,7 +20321,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -20333,7 +20341,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="M258" t="n">
@@ -20352,17 +20360,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -20387,7 +20395,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -20407,7 +20415,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>EPG101</t>
+          <t>EPG111</t>
         </is>
       </c>
       <c r="M259" t="n">
@@ -20426,7 +20434,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>EPG107</t>
+          <t>EPG112</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20436,27 +20444,27 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20481,7 +20489,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>EPG107</t>
+          <t>EPG112</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20502,7 +20510,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>EPG107</t>
+          <t>EPG112</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20512,37 +20520,37 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG112</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -20552,18 +20560,16 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG112</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v/>
       </c>
       <c r="N261" t="n">
         <v/>
@@ -20578,7 +20584,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>EPG107</t>
+          <t>EPG112</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20588,37 +20594,37 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG112</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -20628,18 +20634,16 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG112</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v/>
       </c>
       <c r="N262" t="n">
         <v/>
@@ -20654,7 +20658,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20664,7 +20668,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -20709,16 +20713,18 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
+          <t>EPG514</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
           <t>EPG105</t>
         </is>
-      </c>
-      <c r="N263" t="n">
-        <v/>
       </c>
       <c r="O263" t="n">
         <v/>
@@ -20730,17 +20736,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -20765,7 +20771,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -20785,7 +20791,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -20804,17 +20810,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -20839,7 +20845,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -20859,7 +20865,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>EPG111</t>
+          <t>EPG116</t>
         </is>
       </c>
       <c r="M265" t="n">
@@ -20878,7 +20884,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>EPG112</t>
+          <t>EPG118</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20888,12 +20894,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -20903,12 +20909,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -20933,16 +20939,18 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>EPG112</t>
+          <t>EPG118</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
+          <t>EPG107</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
           <t>EPG105</t>
         </is>
-      </c>
-      <c r="N266" t="n">
-        <v/>
       </c>
       <c r="O266" t="n">
         <v/>
@@ -20954,7 +20962,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>EPG112</t>
+          <t>EPG118</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20964,12 +20972,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -20979,22 +20987,22 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>EPG112</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -21004,19 +21012,23 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>EPG112</t>
-        </is>
-      </c>
-      <c r="M267" t="n">
-        <v/>
-      </c>
-      <c r="N267" t="n">
-        <v/>
+          <t>EPG118</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>EPG107</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="O267" t="n">
         <v/>
@@ -21028,7 +21040,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>EPG112</t>
+          <t>EPG118</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21038,12 +21050,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -21053,22 +21065,22 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>EPG112</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -21078,19 +21090,23 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>EPG112</t>
-        </is>
-      </c>
-      <c r="M268" t="n">
-        <v/>
-      </c>
-      <c r="N268" t="n">
-        <v/>
+          <t>EPG118</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>EPG107</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="O268" t="n">
         <v/>
@@ -21102,7 +21118,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21112,7 +21128,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -21157,12 +21173,12 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>EPG101</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -21180,7 +21196,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21190,7 +21206,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -21215,7 +21231,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -21235,7 +21251,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -21254,7 +21270,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21264,7 +21280,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -21289,7 +21305,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -21309,7 +21325,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>EPG116</t>
+          <t>EPG128</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -21328,7 +21344,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EPG118</t>
+          <t>EPG207</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21338,27 +21354,27 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21383,18 +21399,16 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>EPG118</t>
+          <t>EPG207</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
           <t>EPG105</t>
         </is>
+      </c>
+      <c r="N272" t="n">
+        <v/>
       </c>
       <c r="O272" t="n">
         <v/>
@@ -21406,7 +21420,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>EPG118</t>
+          <t>EPG207</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21416,37 +21430,37 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG207</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -21456,23 +21470,19 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>EPG118</t>
-        </is>
-      </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG207</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
+        <v/>
+      </c>
+      <c r="N273" t="n">
+        <v/>
       </c>
       <c r="O273" t="n">
         <v/>
@@ -21484,7 +21494,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>EPG118</t>
+          <t>EPG207</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21494,37 +21504,37 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG207</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -21534,23 +21544,19 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>EPG118</t>
-        </is>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG207</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
+        <v/>
+      </c>
+      <c r="N274" t="n">
+        <v/>
       </c>
       <c r="O274" t="n">
         <v/>
@@ -21562,7 +21568,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21572,7 +21578,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -21617,18 +21623,16 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>EPG101</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
           <t>EPG105</t>
         </is>
+      </c>
+      <c r="N275" t="n">
+        <v/>
       </c>
       <c r="O275" t="n">
         <v/>
@@ -21640,7 +21644,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21650,7 +21654,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -21675,7 +21679,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -21695,7 +21699,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -21714,7 +21718,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21724,7 +21728,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -21749,7 +21753,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -21769,7 +21773,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>EPG128</t>
+          <t>EPG337</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -21788,7 +21792,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21798,7 +21802,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -21843,7 +21847,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -21864,17 +21868,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -21899,7 +21903,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -21919,7 +21923,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -21938,17 +21942,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -21973,7 +21977,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -21993,7 +21997,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>EPG207</t>
+          <t>EPG339</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -22012,7 +22016,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22022,7 +22026,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -22067,7 +22071,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22088,7 +22092,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22098,7 +22102,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -22123,7 +22127,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -22143,7 +22147,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="M282" t="n">
@@ -22162,7 +22166,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22172,7 +22176,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -22197,7 +22201,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -22217,7 +22221,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>EPG337</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="M283" t="n">
@@ -22236,17 +22240,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -22271,12 +22275,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -22286,18 +22290,16 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>EPG339</t>
-        </is>
-      </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG402</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v/>
       </c>
       <c r="N284" t="n">
         <v/>
@@ -22312,7 +22314,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22322,7 +22324,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -22347,7 +22349,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -22367,7 +22369,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG402</t>
         </is>
       </c>
       <c r="M285" t="n">
@@ -22386,7 +22388,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG405</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22396,7 +22398,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -22421,7 +22423,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG405</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -22441,7 +22443,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>EPG339</t>
+          <t>EPG405</t>
         </is>
       </c>
       <c r="M286" t="n">
@@ -22460,17 +22462,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG405</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -22495,12 +22497,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG405</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -22510,18 +22512,16 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>EPG402</t>
-        </is>
-      </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG405</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v/>
       </c>
       <c r="N287" t="n">
         <v/>
@@ -22536,17 +22536,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG405</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -22571,12 +22571,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -22586,16 +22586,18 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>EPG402</t>
-        </is>
-      </c>
-      <c r="M288" t="n">
-        <v/>
+          <t>EPG405</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="N288" t="n">
         <v/>
@@ -22610,22 +22612,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG406</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22635,22 +22637,22 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -22660,19 +22662,23 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>EPG402</t>
-        </is>
-      </c>
-      <c r="M289" t="n">
-        <v/>
-      </c>
-      <c r="N289" t="n">
-        <v/>
+          <t>EPG406</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>UXFP08</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="O289" t="n">
         <v/>
@@ -22684,7 +22690,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG406</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22694,12 +22700,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -22709,22 +22715,22 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -22734,19 +22740,23 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>EPG402</t>
-        </is>
-      </c>
-      <c r="M290" t="n">
-        <v/>
-      </c>
-      <c r="N290" t="n">
-        <v/>
+          <t>EPG406</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>UXFP08</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="O290" t="n">
         <v/>
@@ -22758,7 +22768,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG406</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -22768,12 +22778,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -22783,22 +22793,22 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>EPG402</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -22808,19 +22818,23 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>EPG402</t>
-        </is>
-      </c>
-      <c r="M291" t="n">
-        <v/>
-      </c>
-      <c r="N291" t="n">
-        <v/>
+          <t>EPG406</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>UXFP08</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="O291" t="n">
         <v/>
@@ -22832,22 +22846,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>EPG405</t>
+          <t>EPG505</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -22857,22 +22871,22 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>EPG405</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -22882,16 +22896,18 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>EPG405</t>
-        </is>
-      </c>
-      <c r="M292" t="n">
-        <v/>
+          <t>EPG505</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="N292" t="n">
         <v/>
@@ -22906,22 +22922,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>EPG405</t>
+          <t>EPG505</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -22931,22 +22947,22 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>EPG405</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -22956,16 +22972,18 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>EPG405</t>
-        </is>
-      </c>
-      <c r="M293" t="n">
-        <v/>
+          <t>EPG505</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>EPG105</t>
+        </is>
       </c>
       <c r="N293" t="n">
         <v/>
@@ -22980,22 +22998,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>EPG405</t>
+          <t>EPG505</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -23005,12 +23023,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -23035,7 +23053,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>EPG405</t>
+          <t>EPG505</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -23056,7 +23074,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>EPG406</t>
+          <t>EPG514</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23066,27 +23084,27 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -23111,18 +23129,16 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>EPG406</t>
+          <t>EPG514</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>UXFP08</t>
-        </is>
-      </c>
-      <c r="N295" t="inlineStr">
-        <is>
           <t>EPG105</t>
         </is>
+      </c>
+      <c r="N295" t="n">
+        <v/>
       </c>
       <c r="O295" t="n">
         <v/>
@@ -23134,7 +23150,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>EPG406</t>
+          <t>EPG514</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -23144,37 +23160,37 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG514</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -23184,23 +23200,19 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>EPG406</t>
-        </is>
-      </c>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>UXFP08</t>
-        </is>
-      </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG514</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v/>
+      </c>
+      <c r="N296" t="n">
+        <v/>
       </c>
       <c r="O296" t="n">
         <v/>
@@ -23212,7 +23224,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EPG406</t>
+          <t>EPG514</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -23222,37 +23234,37 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>EPG514</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -23262,23 +23274,19 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>EPG406</t>
-        </is>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>UXFP08</t>
-        </is>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>EPG514</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v/>
+      </c>
+      <c r="N297" t="n">
+        <v/>
       </c>
       <c r="O297" t="n">
         <v/>
@@ -23290,7 +23298,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>EPG505</t>
+          <t>EPG522</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -23300,7 +23308,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -23345,16 +23353,18 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>EPG505</t>
+          <t>EPG522</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
+          <t>EPG107</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
           <t>EPG105</t>
         </is>
-      </c>
-      <c r="N298" t="n">
-        <v/>
       </c>
       <c r="O298" t="n">
         <v/>
@@ -23366,7 +23376,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>EPG505</t>
+          <t>EPG522</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -23376,7 +23386,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -23421,16 +23431,18 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>EPG505</t>
+          <t>EPG522</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
+          <t>EPG107</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
           <t>EPG105</t>
         </is>
-      </c>
-      <c r="N299" t="n">
-        <v/>
       </c>
       <c r="O299" t="n">
         <v/>
@@ -23442,7 +23454,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>EPG505</t>
+          <t>EPG522</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -23452,7 +23464,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -23497,16 +23509,18 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>EPG505</t>
+          <t>EPG522</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
+          <t>EPG107</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
           <t>EPG105</t>
         </is>
-      </c>
-      <c r="N300" t="n">
-        <v/>
       </c>
       <c r="O300" t="n">
         <v/>
@@ -23518,7 +23532,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>HXUD01</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -23528,12 +23542,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -23543,17 +23557,17 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -23573,19 +23587,23 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>HXUD01</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>EPG105</t>
-        </is>
-      </c>
-      <c r="N301" t="n">
-        <v/>
-      </c>
-      <c r="O301" t="n">
-        <v/>
+          <t>DJQF04</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>JXHV01</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="P301" t="n">
         <v/>
@@ -23594,7 +23612,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>HXUD01</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -23604,12 +23622,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -23619,22 +23637,22 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -23644,22 +23662,28 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>EPG514</t>
-        </is>
-      </c>
-      <c r="M302" t="n">
-        <v/>
-      </c>
-      <c r="N302" t="n">
-        <v/>
-      </c>
-      <c r="O302" t="n">
-        <v/>
+          <t>HXUD01</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>DJQF04</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>JXHV01</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="P302" t="n">
         <v/>
@@ -23668,7 +23692,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>HXUD01</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -23678,12 +23702,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -23693,22 +23717,22 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>EPG514</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -23718,22 +23742,28 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>EPG514</t>
-        </is>
-      </c>
-      <c r="M303" t="n">
-        <v/>
-      </c>
-      <c r="N303" t="n">
-        <v/>
-      </c>
-      <c r="O303" t="n">
-        <v/>
+          <t>HXUD01</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>DJQF04</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>JXHV01</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="P303" t="n">
         <v/>
@@ -23742,7 +23772,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>EPG522</t>
+          <t>JFH102</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -23752,7 +23782,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -23777,7 +23807,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -23797,18 +23827,16 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>EPG522</t>
+          <t>JFH102</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>ZMA105</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v/>
       </c>
       <c r="O304" t="n">
         <v/>
@@ -23820,7 +23848,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>EPG522</t>
+          <t>JFH102</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -23830,7 +23858,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -23855,7 +23883,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -23875,18 +23903,16 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>EPG522</t>
+          <t>JFH102</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>ZMA105</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v/>
       </c>
       <c r="O305" t="n">
         <v/>
@@ -23898,7 +23924,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EPG522</t>
+          <t>JFH102</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -23908,7 +23934,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -23933,7 +23959,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -23953,18 +23979,16 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>EPG522</t>
+          <t>JFH102</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>EPG107</t>
-        </is>
-      </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>EPG105</t>
-        </is>
+          <t>ZMA105</t>
+        </is>
+      </c>
+      <c r="N306" t="n">
+        <v/>
       </c>
       <c r="O306" t="n">
         <v/>
@@ -23976,7 +24000,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>HXUD01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -23986,7 +24010,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -24031,23 +24055,19 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>HXUD01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>DJQF04</t>
-        </is>
-      </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>JXHV01</t>
-        </is>
-      </c>
-      <c r="O307" t="inlineStr">
-        <is>
           <t>ZMA105</t>
         </is>
+      </c>
+      <c r="N307" t="n">
+        <v/>
+      </c>
+      <c r="O307" t="n">
+        <v/>
       </c>
       <c r="P307" t="n">
         <v/>
@@ -24056,7 +24076,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>HXUD01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -24066,7 +24086,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -24111,23 +24131,19 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>HXUD01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>DJQF04</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>JXHV01</t>
-        </is>
-      </c>
-      <c r="O308" t="inlineStr">
-        <is>
           <t>ZMA105</t>
         </is>
+      </c>
+      <c r="N308" t="n">
+        <v/>
+      </c>
+      <c r="O308" t="n">
+        <v/>
       </c>
       <c r="P308" t="n">
         <v/>
@@ -24136,7 +24152,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>HXUD01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -24146,7 +24162,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -24191,23 +24207,19 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>HXUD01</t>
+          <t>JXHV01</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>DJQF04</t>
-        </is>
-      </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>JXHV01</t>
-        </is>
-      </c>
-      <c r="O309" t="inlineStr">
-        <is>
           <t>ZMA105</t>
         </is>
+      </c>
+      <c r="N309" t="n">
+        <v/>
+      </c>
+      <c r="O309" t="n">
+        <v/>
       </c>
       <c r="P309" t="n">
         <v/>
@@ -24216,7 +24228,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>KGZK01</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -24226,7 +24238,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -24266,21 +24278,23 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>Back engineered to ZMA105 via physical graph</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>KGZK01</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
+          <t>DJQF03</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
           <t>ZMA105</t>
         </is>
-      </c>
-      <c r="N310" t="n">
-        <v/>
       </c>
       <c r="O310" t="n">
         <v/>
@@ -24292,7 +24306,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>KGZK01</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -24302,7 +24316,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -24337,38 +24351,36 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Incomplete</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>Followed 2G Route | Mis-Configured Route</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>KGZK01</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
+          <t>DJQF03</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
           <t>ZMA105</t>
         </is>
       </c>
-      <c r="N311" t="n">
-        <v/>
-      </c>
-      <c r="O311" t="n">
-        <v/>
-      </c>
-      <c r="P311" t="n">
-        <v/>
-      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>KGZK01</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -24378,7 +24390,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -24413,38 +24425,36 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Incomplete</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>Followed 2G Route | Mis-Configured Route</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>JFH102</t>
+          <t>KGZK01</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
+          <t>DJQF03</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
           <t>ZMA105</t>
         </is>
       </c>
-      <c r="N312" t="n">
-        <v/>
-      </c>
-      <c r="O312" t="n">
-        <v/>
-      </c>
-      <c r="P312" t="n">
-        <v/>
-      </c>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>JXHV01</t>
+          <t>PGEF01</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -24454,7 +24464,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -24499,7 +24509,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>JXHV01</t>
+          <t>PGEF01</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -24520,7 +24530,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>JXHV01</t>
+          <t>PGEF01</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -24530,7 +24540,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -24575,7 +24585,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>JXHV01</t>
+          <t>PGEF01</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -24596,7 +24606,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>JXHV01</t>
+          <t>PGEF01</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -24606,7 +24616,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -24651,7 +24661,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>JXHV01</t>
+          <t>PGEF01</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -24672,47 +24682,47 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>ROM313</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>ROM313</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -24722,23 +24732,19 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Back engineered to ZMA105 via physical graph</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>KGZK01</t>
-        </is>
-      </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>ROM313</t>
+        </is>
+      </c>
+      <c r="M316" t="n">
+        <v/>
+      </c>
+      <c r="N316" t="n">
+        <v/>
       </c>
       <c r="O316" t="n">
         <v/>
@@ -24750,91 +24756,91 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>ROM313</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>ROM313</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Followed 2G Route | Mis-Configured Route</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>KGZK01</t>
-        </is>
-      </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
+          <t>ROM313</t>
+        </is>
+      </c>
+      <c r="M317" t="n">
+        <v/>
+      </c>
+      <c r="N317" t="n">
+        <v/>
+      </c>
+      <c r="O317" t="n">
+        <v/>
+      </c>
+      <c r="P317" t="n">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>UXFP08</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -24859,7 +24865,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -24869,46 +24875,48 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Followed 2G Route | Mis-Configured Route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>KGZK01</t>
+          <t>UXFP08</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>DJQF03</t>
-        </is>
-      </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="O318" t="inlineStr"/>
-      <c r="P318" t="inlineStr"/>
+          <t>EPG105</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v/>
+      </c>
+      <c r="O318" t="n">
+        <v/>
+      </c>
+      <c r="P318" t="n">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PGEF01</t>
+          <t>UXFP08</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -24933,7 +24941,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -24953,12 +24961,12 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>PGEF01</t>
+          <t>UXFP08</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="N319" t="n">
@@ -24974,17 +24982,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>PGEF01</t>
+          <t>UXFP08</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -25009,7 +25017,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -25029,12 +25037,12 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>PGEF01</t>
+          <t>UXFP08</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>EPG105</t>
         </is>
       </c>
       <c r="N320" t="n">
@@ -25050,47 +25058,47 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>PGEF01</t>
+          <t>WMZF03</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
+          <t>FTTT-Hub</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Hub</t>
+          <t>FTTT-Hub</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>FTTT</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>ZMA105</t>
+          <t>WMZF03</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Ring (Built)</t>
+          <t>Not in OFN Sheet (Built)</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -25100,18 +25108,16 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Followed NMS-DIR</t>
+          <t>FTTT self-terminating route</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>PGEF01</t>
-        </is>
-      </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
+          <t>WMZF03</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
+        <v/>
       </c>
       <c r="N321" t="n">
         <v/>
@@ -25126,17 +25132,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ROM313</t>
+          <t>WMZF03</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -25161,7 +25167,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>ROM313</t>
+          <t>WMZF03</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -25181,7 +25187,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>ROM313</t>
+          <t>WMZF03</t>
         </is>
       </c>
       <c r="M322" t="n">
@@ -25200,22 +25206,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ROM313</t>
+          <t>ZMA102</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -25225,22 +25231,22 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>ROM313</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -25250,16 +25256,18 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>ROM313</t>
-        </is>
-      </c>
-      <c r="M323" t="n">
-        <v/>
+          <t>ZMA102</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>ZMA105</t>
+        </is>
       </c>
       <c r="N323" t="n">
         <v/>
@@ -25274,17 +25282,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>UXFP08</t>
+          <t>ZMA102</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -25309,7 +25317,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -25329,12 +25337,12 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>UXFP08</t>
+          <t>ZMA102</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="N324" t="n">
@@ -25350,17 +25358,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>UXFP08</t>
+          <t>ZMA102</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -25385,7 +25393,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -25405,12 +25413,12 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>UXFP08</t>
+          <t>ZMA102</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZMA105</t>
         </is>
       </c>
       <c r="N325" t="n">
@@ -25426,17 +25434,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>UXFP08</t>
+          <t>ZMA106</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -25461,7 +25469,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZZXE01</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -25481,12 +25489,12 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>UXFP08</t>
+          <t>ZMA106</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>EPG105</t>
+          <t>ZZXE01</t>
         </is>
       </c>
       <c r="N326" t="n">
@@ -25502,7 +25510,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>WMZF03</t>
+          <t>ZMA106</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -25512,12 +25520,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -25527,22 +25535,22 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>WMZF03</t>
+          <t>ZZXE01</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
@@ -25552,16 +25560,18 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>WMZF03</t>
-        </is>
-      </c>
-      <c r="M327" t="n">
-        <v/>
+          <t>ZMA106</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>ZZXE01</t>
+        </is>
       </c>
       <c r="N327" t="n">
         <v/>
@@ -25576,7 +25586,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>WMZF03</t>
+          <t>ZMA106</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -25586,12 +25596,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -25601,22 +25611,22 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>FTTT-Hub</t>
+          <t>Hub</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>FTTT</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>WMZF03</t>
+          <t>ZZXE01</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Not in OFN Sheet (Built)</t>
+          <t>Ring (Built)</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -25626,16 +25636,18 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>FTTT self-terminating route</t>
+          <t>Followed NMS-DIR</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>WMZF03</t>
-        </is>
-      </c>
-      <c r="M328" t="n">
-        <v/>
+          <t>ZMA106</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>ZZXE01</t>
+        </is>
       </c>
       <c r="N328" t="n">
         <v/>
@@ -25650,7 +25662,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ZMA102</t>
+          <t>ZMA107</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -25660,7 +25672,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -25705,7 +25717,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>ZMA102</t>
+          <t>ZMA107</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -25726,7 +25738,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ZMA102</t>
+          <t>ZMA107</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -25736,7 +25748,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -25781,7 +25793,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>ZMA102</t>
+          <t>ZMA107</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -25802,7 +25814,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ZMA102</t>
+          <t>ZMA107</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -25812,7 +25824,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -25857,7 +25869,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>ZMA102</t>
+          <t>ZMA107</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -25872,462 +25884,6 @@
         <v/>
       </c>
       <c r="P331" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>ZMA106</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2G</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>ZZXE01</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>Ring (Built)</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Followed NMS-DIR</t>
-        </is>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>ZMA106</t>
-        </is>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>ZZXE01</t>
-        </is>
-      </c>
-      <c r="N332" t="n">
-        <v/>
-      </c>
-      <c r="O332" t="n">
-        <v/>
-      </c>
-      <c r="P332" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>ZMA106</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>3G</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>ZZXE01</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>Ring (Built)</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Followed NMS-DIR</t>
-        </is>
-      </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>ZMA106</t>
-        </is>
-      </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>ZZXE01</t>
-        </is>
-      </c>
-      <c r="N333" t="n">
-        <v/>
-      </c>
-      <c r="O333" t="n">
-        <v/>
-      </c>
-      <c r="P333" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>ZMA106</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>4G</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>ZZXE01</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>Ring (Built)</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Followed NMS-DIR</t>
-        </is>
-      </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>ZMA106</t>
-        </is>
-      </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>ZZXE01</t>
-        </is>
-      </c>
-      <c r="N334" t="n">
-        <v/>
-      </c>
-      <c r="O334" t="n">
-        <v/>
-      </c>
-      <c r="P334" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>ZMA107</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2G</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>Ring (Built)</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>Followed NMS-DIR</t>
-        </is>
-      </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>ZMA107</t>
-        </is>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="N335" t="n">
-        <v/>
-      </c>
-      <c r="O335" t="n">
-        <v/>
-      </c>
-      <c r="P335" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>ZMA107</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>3G</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>Ring (Built)</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Followed NMS-DIR</t>
-        </is>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>ZMA107</t>
-        </is>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="N336" t="n">
-        <v/>
-      </c>
-      <c r="O336" t="n">
-        <v/>
-      </c>
-      <c r="P336" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>ZMA107</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>4G</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Hub</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>Ring (Built)</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Followed NMS-DIR</t>
-        </is>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>ZMA107</t>
-        </is>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>ZMA105</t>
-        </is>
-      </c>
-      <c r="N337" t="n">
-        <v/>
-      </c>
-      <c r="O337" t="n">
-        <v/>
-      </c>
-      <c r="P337" t="n">
         <v/>
       </c>
     </row>
